--- a/output/pdf_financials_xlsx/NVPC.xlsx
+++ b/output/pdf_financials_xlsx/NVPC.xlsx
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.3413</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.957714</v>
       </c>
     </row>
     <row r="93">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.567288</v>
+        <v>0.418092</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.358345</v>
       </c>
     </row>
     <row r="119">
@@ -2574,7 +2574,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.3413</v>
       </c>
@@ -2998,7 +3002,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.149196</v>
       </c>

--- a/output/pdf_financials_xlsx/NVPC.xlsx
+++ b/output/pdf_financials_xlsx/NVPC.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.038766</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.429069</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.038766</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.429069</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.051657</v>
+        <v>0.012891</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.523645</v>
+        <v>0.09457599999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NVPC.xlsx
+++ b/output/pdf_financials_xlsx/NVPC.xlsx
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011453</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.23539</v>
       </c>
     </row>
     <row r="102">
@@ -2894,7 +2894,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-0.011453</v>
       </c>
